--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.8534506898532</v>
+        <v>4.526185737101146</v>
       </c>
       <c r="D2" t="n">
-        <v>13.66339890553686</v>
+        <v>2.22030232214974</v>
       </c>
       <c r="E2" t="n">
-        <v>7.494967996322019</v>
+        <v>1.217932299402328</v>
       </c>
       <c r="F2" t="n">
-        <v>9.467177911001187</v>
+        <v>1.538416410537693</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.62397516846361</v>
+        <v>4.976395964875337</v>
       </c>
       <c r="D3" t="n">
-        <v>20.23215161629292</v>
+        <v>3.287724637647599</v>
       </c>
       <c r="E3" t="n">
-        <v>7.494967996322019</v>
+        <v>1.217932299402328</v>
       </c>
       <c r="F3" t="n">
-        <v>9.467177911001187</v>
+        <v>1.538416410537693</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.91399550446486</v>
+        <v>2.586024269475539</v>
       </c>
       <c r="D4" t="n">
-        <v>16.15570376162427</v>
+        <v>2.625301861263944</v>
       </c>
       <c r="E4" t="n">
-        <v>7.494967996322019</v>
+        <v>1.217932299402328</v>
       </c>
       <c r="F4" t="n">
-        <v>9.467177911001187</v>
+        <v>1.538416410537693</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.13624639221517</v>
+        <v>5.059640038734966</v>
       </c>
       <c r="D5" t="n">
-        <v>32.22477837210788</v>
+        <v>5.236526485467531</v>
       </c>
       <c r="E5" t="n">
-        <v>7.494967996322019</v>
+        <v>1.217932299402328</v>
       </c>
       <c r="F5" t="n">
-        <v>9.467177911001187</v>
+        <v>1.538416410537693</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.87198876802157</v>
+        <v>6.479198174803504</v>
       </c>
       <c r="D6" t="n">
-        <v>40.91759575378705</v>
+        <v>6.649109309990395</v>
       </c>
       <c r="E6" t="n">
-        <v>7.494967996322019</v>
+        <v>1.217932299402328</v>
       </c>
       <c r="F6" t="n">
-        <v>9.467177911001187</v>
+        <v>1.538416410537693</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.22834953831035</v>
+        <v>3.612106799975431</v>
       </c>
       <c r="D7" t="n">
-        <v>22.6254937692111</v>
+        <v>3.676642737496803</v>
       </c>
       <c r="E7" t="n">
-        <v>7.494967996322019</v>
+        <v>1.217932299402328</v>
       </c>
       <c r="F7" t="n">
-        <v>9.467177911001187</v>
+        <v>1.538416410537693</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
